--- a/input/Studies/MEET2/SepOverpressure.xlsx
+++ b/input/Studies/MEET2/SepOverpressure.xlsx
@@ -2145,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2449,6 +2449,16 @@
           <t>Factor Tag</t>
         </is>
       </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>CCEE Ratio Distribution</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Crankcase Emissions Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2633,6 +2643,12 @@
         <is>
           <t>ts_compressor</t>
         </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BD2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
